--- a/cucumber-for-appian/src/test/resources/testdata/Regression/04_SMB_Regression.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/Regression/04_SMB_Regression.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="232">
   <si>
     <t>ScenarioId</t>
   </si>
@@ -377,6 +377,9 @@
     <t>Reason for Decline</t>
   </si>
   <si>
+    <t>Do you have a specific medical, office or other business equipment in mind?</t>
+  </si>
+  <si>
     <t>Is the medical, office or other business equipment new?</t>
   </si>
   <si>
@@ -404,33 +407,60 @@
     <t>Used</t>
   </si>
   <si>
+    <t>Dealer</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Finance Lease without Services</t>
+  </si>
+  <si>
+    <t>Telephone systems</t>
+  </si>
+  <si>
+    <t>Toyota Hatch</t>
+  </si>
+  <si>
     <t>NA</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Finance Lease without Services</t>
-  </si>
-  <si>
-    <t>Telephone systems</t>
-  </si>
-  <si>
     <t>$250,000</t>
   </si>
   <si>
     <t>$1,500</t>
   </si>
   <si>
-    <t>$500</t>
-  </si>
-  <si>
     <t>monthly in Arrears</t>
   </si>
   <si>
     <t>48 months</t>
   </si>
   <si>
+    <t>TOYOTA</t>
+  </si>
+  <si>
+    <t>BZ4X</t>
+  </si>
+  <si>
+    <t>71kWh AWD</t>
+  </si>
+  <si>
+    <t>AUDIA1VIN12345678</t>
+  </si>
+  <si>
+    <t>AUDIA1REG123456</t>
+  </si>
+  <si>
+    <t>TOYOTAENG123456</t>
+  </si>
+  <si>
+    <t>Comments: TOYOTA Passenger cars including electric vehicles</t>
+  </si>
+  <si>
+    <t>New Application[2]</t>
+  </si>
+  <si>
     <t>45 Malonga Ave, Kellyville NSW 2155</t>
   </si>
   <si>
@@ -446,190 +476,255 @@
     <t>DAIRY PRODUCT ADVERTISEMENT</t>
   </si>
   <si>
+    <t>27/05/1981</t>
+  </si>
+  <si>
+    <t>Car Licence (C)</t>
+  </si>
+  <si>
     <t>No</t>
   </si>
   <si>
+    <t>C:\Users\HP\Downloads\Rental_Agreement_Document.pdf</t>
+  </si>
+  <si>
     <t>C:\Users\HP\Downloads\DealerQuote.pdf</t>
   </si>
   <si>
     <t>TC002</t>
   </si>
   <si>
+    <t>Cameras</t>
+  </si>
+  <si>
+    <t>71KWH AWD</t>
+  </si>
+  <si>
+    <t>WD HOMES SERVICES</t>
+  </si>
+  <si>
+    <t>56 Kimbler Rd, Roma QLD 4455</t>
+  </si>
+  <si>
+    <t>C MANUFACTURING</t>
+  </si>
+  <si>
+    <t>113 Dairy Product Manufacturing</t>
+  </si>
+  <si>
+    <t>Dean</t>
+  </si>
+  <si>
+    <t>Jensen</t>
+  </si>
+  <si>
+    <t>Winchester</t>
+  </si>
+  <si>
+    <t>NZ Citizen</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Renting</t>
+  </si>
+  <si>
+    <t>chandu.nagu+60@gmail.com</t>
+  </si>
+  <si>
+    <t>Learners Permit</t>
+  </si>
+  <si>
+    <t>QLD</t>
+  </si>
+  <si>
+    <t>YES, I DO HAVE SUFFICIENT ONGOING MONTHLY CASHFLOW TO MEET MY REPAYMENTS UNDER THIS FACILITY.</t>
+  </si>
+  <si>
+    <t>$30,000</t>
+  </si>
+  <si>
+    <t>Monthly</t>
+  </si>
+  <si>
+    <t>$2,000</t>
+  </si>
+  <si>
+    <t>Select All Privacy Consent check boxes</t>
+  </si>
+  <si>
+    <t>${TC001.Application Number}</t>
+  </si>
+  <si>
+    <t>${TC001.Quote Number}</t>
+  </si>
+  <si>
+    <t>${TC001.Client or Applicant}</t>
+  </si>
+  <si>
+    <t>${TC001.Last Updated User}</t>
+  </si>
+  <si>
+    <t>SMBone Specialist</t>
+  </si>
+  <si>
+    <t>$58,225.00</t>
+  </si>
+  <si>
+    <t>01/01/2021</t>
+  </si>
+  <si>
+    <t>$16,800.00</t>
+  </si>
+  <si>
+    <t>$78,876.84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$1,029.11
+</t>
+  </si>
+  <si>
+    <t>Advance</t>
+  </si>
+  <si>
+    <t>Private Sale</t>
+  </si>
+  <si>
+    <t>Passenger or Light Commercial Vehicle</t>
+  </si>
+  <si>
+    <t>$0.50</t>
+  </si>
+  <si>
+    <t>2.68%</t>
+  </si>
+  <si>
+    <t>30.00%</t>
+  </si>
+  <si>
+    <t>Proceeded</t>
+  </si>
+  <si>
+    <t>Download</t>
+  </si>
+  <si>
+    <t>Declined</t>
+  </si>
+  <si>
+    <t>others</t>
+  </si>
+  <si>
+    <t>TC003</t>
+  </si>
+  <si>
     <t>SINGH, JATINDER</t>
   </si>
   <si>
     <t>Sole Trader</t>
   </si>
   <si>
-    <t>Passenger or Light Commercial Vehicle</t>
-  </si>
-  <si>
-    <t>Yes, it is for a new asset</t>
+    <t>Passenger cars including electric vehicles</t>
+  </si>
+  <si>
+    <t>Ebony</t>
+  </si>
+  <si>
+    <t>Grey Synthetic leather</t>
+  </si>
+  <si>
+    <t>$56,000</t>
+  </si>
+  <si>
+    <t>$1,000</t>
+  </si>
+  <si>
+    <t>monthly in advance</t>
+  </si>
+  <si>
+    <t>Roadside Assistance</t>
+  </si>
+  <si>
+    <t>NSW</t>
+  </si>
+  <si>
+    <t>$10,000.00</t>
+  </si>
+  <si>
+    <t>APP-753</t>
+  </si>
+  <si>
+    <t>SMB-00001109
+SMB-00001109</t>
+  </si>
+  <si>
+    <t>Processing</t>
+  </si>
+  <si>
+    <t>01 Apr 2026 09:10 PM</t>
+  </si>
+  <si>
+    <t>Automation Introducer</t>
+  </si>
+  <si>
+    <t>TC004</t>
+  </si>
+  <si>
+    <t>New</t>
   </si>
   <si>
     <t>Chattel Mortgage</t>
   </si>
   <si>
-    <t>Passenger cars including electric vehicles</t>
-  </si>
-  <si>
-    <t>Toyota Hatch</t>
-  </si>
-  <si>
-    <t>$56,000</t>
-  </si>
-  <si>
-    <t>$0.00</t>
-  </si>
-  <si>
-    <t>$1,000</t>
-  </si>
-  <si>
-    <t>Monthly in Advance</t>
-  </si>
-  <si>
-    <t>Fuel Card</t>
-  </si>
-  <si>
-    <t>36 Months</t>
-  </si>
-  <si>
-    <t>TOYOTA</t>
-  </si>
-  <si>
-    <t>BZ4X</t>
-  </si>
-  <si>
-    <t>71kWh AWD</t>
-  </si>
-  <si>
-    <t>TOYOTAVIN12345678</t>
-  </si>
-  <si>
-    <t>TOYOTAREG123456</t>
-  </si>
-  <si>
-    <t>TOYOTAENG123456</t>
-  </si>
-  <si>
-    <t>Comments: TOYOTA Passenger cars including electric vehicles</t>
-  </si>
-  <si>
-    <t>New Application[2]</t>
-  </si>
-  <si>
-    <t>WD HOMES SERVICES</t>
-  </si>
-  <si>
-    <t>56 Kimbler Rd, Roma QLD 4455</t>
-  </si>
-  <si>
-    <t>C MANUFACTURING</t>
-  </si>
-  <si>
-    <t>113 Dairy Product Manufacturing</t>
-  </si>
-  <si>
-    <t>Dean</t>
-  </si>
-  <si>
-    <t>Jensen</t>
-  </si>
-  <si>
-    <t>Winchester</t>
-  </si>
-  <si>
-    <t>NZ Citizen</t>
-  </si>
-  <si>
-    <t>27/05/1981</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>Renting</t>
-  </si>
-  <si>
-    <t>chandu.nagu+60@gmail.com</t>
-  </si>
-  <si>
-    <t>Learners Permit</t>
-  </si>
-  <si>
-    <t>Car Licence (C)</t>
-  </si>
-  <si>
-    <t>QLD</t>
-  </si>
-  <si>
-    <t>$30,000</t>
-  </si>
-  <si>
-    <t>Monthly</t>
-  </si>
-  <si>
-    <t>$2,000</t>
-  </si>
-  <si>
-    <t>Select All Privacy Consent check boxes</t>
-  </si>
-  <si>
-    <t>${TC001.Application Number}</t>
-  </si>
-  <si>
-    <t>${TC001.Quote Number}</t>
-  </si>
-  <si>
-    <t>${TC001.Client or Applicant}</t>
-  </si>
-  <si>
-    <t>${TC001.Last Updated User}</t>
-  </si>
-  <si>
-    <t>SMBone Specialist</t>
-  </si>
-  <si>
-    <t>$58,225.00</t>
-  </si>
-  <si>
-    <t>01/01/2021</t>
-  </si>
-  <si>
-    <t>$16,800.00</t>
-  </si>
-  <si>
-    <t>$68,122.30</t>
-  </si>
-  <si>
-    <t>$1,420.12</t>
-  </si>
-  <si>
-    <t>Advance</t>
+    <t>$100.00</t>
+  </si>
+  <si>
+    <t>60 months</t>
+  </si>
+  <si>
+    <t>$5,000.00</t>
+  </si>
+  <si>
+    <t>${TC003.Application Number}</t>
+  </si>
+  <si>
+    <t>${TC003.Quote Number}</t>
+  </si>
+  <si>
+    <t>${TC003.Client or Applicant}</t>
+  </si>
+  <si>
+    <t>${TC003.Last Updated User}</t>
+  </si>
+  <si>
+    <t>$72,053.37</t>
+  </si>
+  <si>
+    <t>$76,252.61</t>
+  </si>
+  <si>
+    <t>$1,145.61</t>
+  </si>
+  <si>
+    <t>$1,129.88</t>
   </si>
   <si>
     <t>Dealer Pricing</t>
   </si>
   <si>
-    <t>$0.50</t>
-  </si>
-  <si>
-    <t>2.68%</t>
-  </si>
-  <si>
-    <t>30.00%</t>
-  </si>
-  <si>
-    <t>Proceeded</t>
-  </si>
-  <si>
-    <t>Download</t>
-  </si>
-  <si>
-    <t>Declined</t>
-  </si>
-  <si>
-    <t>others</t>
+    <t>$102.72</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>37.43%</t>
+  </si>
+  <si>
+    <t>Conditional Approval</t>
+  </si>
+  <si>
+    <t>Copy of current council rates notice to be provided to confirm property ownership.</t>
   </si>
   <si>
     <r>
@@ -660,84 +755,6 @@
       </rPr>
       <t>' document.</t>
     </r>
-  </si>
-  <si>
-    <t>TC003</t>
-  </si>
-  <si>
-    <t>Ebony</t>
-  </si>
-  <si>
-    <t>Grey Synthetic leather</t>
-  </si>
-  <si>
-    <t>monthly in advance</t>
-  </si>
-  <si>
-    <t>Roadside Assistance</t>
-  </si>
-  <si>
-    <t>NSW</t>
-  </si>
-  <si>
-    <t>$10,000.00</t>
-  </si>
-  <si>
-    <t>AUDIA1VIN12345678</t>
-  </si>
-  <si>
-    <t>AUDIA1REG123456</t>
-  </si>
-  <si>
-    <t>YES, I DO HAVE SUFFICIENT ONGOING MONTHLY CASHFLOW TO MEET MY REPAYMENTS UNDER THIS FACILITY.</t>
-  </si>
-  <si>
-    <t>C:\Users\HP\Downloads\Rental_Agreement_Document.pdf</t>
-  </si>
-  <si>
-    <t>TC004</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>Dealer</t>
-  </si>
-  <si>
-    <t>71KWH AWD</t>
-  </si>
-  <si>
-    <t>${TC003.Application Number}</t>
-  </si>
-  <si>
-    <t>${TC003.Quote Number}</t>
-  </si>
-  <si>
-    <t>${TC003.Client or Applicant}</t>
-  </si>
-  <si>
-    <t>${TC003.Last Updated User}</t>
-  </si>
-  <si>
-    <t>$72,053.37</t>
-  </si>
-  <si>
-    <t>$671,875.80</t>
-  </si>
-  <si>
-    <t>$1,145.61</t>
-  </si>
-  <si>
-    <t>$15,524.74</t>
-  </si>
-  <si>
-    <t>54.32%</t>
-  </si>
-  <si>
-    <t>Conditional Approval</t>
-  </si>
-  <si>
-    <t>Copy of current council rates notice to be provided to confirm property ownership.</t>
   </si>
 </sst>
 </file>
@@ -1426,10 +1443,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1443,8 +1460,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1465,9 +1482,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1821,104 +1835,131 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:DP25"/>
+  <dimension ref="A1:DQ23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.11111111111111" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="16.8888888888889" customWidth="1"/>
-    <col min="4" max="4" width="8.11111111111111" customWidth="1"/>
-    <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="16.3333333333333" customWidth="1"/>
-    <col min="7" max="7" width="12.7777777777778" customWidth="1"/>
-    <col min="8" max="8" width="16.3333333333333" customWidth="1"/>
-    <col min="9" max="9" width="9.77777777777778" customWidth="1"/>
-    <col min="10" max="10" width="19.3333333333333" customWidth="1"/>
-    <col min="11" max="12" width="8.44444444444444" customWidth="1"/>
-    <col min="13" max="13" width="9.55555555555556" customWidth="1"/>
-    <col min="14" max="14" width="17.5555555555556" customWidth="1"/>
-    <col min="15" max="15" width="10.7777777777778" customWidth="1"/>
-    <col min="16" max="16" width="10.8888888888889" customWidth="1"/>
-    <col min="17" max="17" width="14.5555555555556" customWidth="1"/>
-    <col min="18" max="18" width="6.88888888888889" customWidth="1"/>
-    <col min="19" max="19" width="5.77777777777778" customWidth="1"/>
-    <col min="20" max="20" width="6.77777777777778" customWidth="1"/>
-    <col min="21" max="21" width="12.6666666666667" customWidth="1"/>
-    <col min="22" max="22" width="8.33333333333333" customWidth="1"/>
-    <col min="23" max="23" width="11.6666666666667" customWidth="1"/>
-    <col min="24" max="24" width="9.11111111111111" customWidth="1"/>
-    <col min="25" max="25" width="19.6666666666667" customWidth="1"/>
-    <col min="26" max="26" width="15.5555555555556" customWidth="1"/>
-    <col min="27" max="34" width="6.55555555555556" customWidth="1"/>
-    <col min="35" max="35" width="7.66666666666667" customWidth="1"/>
-    <col min="37" max="37" width="8.55555555555556" customWidth="1"/>
-    <col min="38" max="39" width="8.44444444444444" customWidth="1"/>
-    <col min="40" max="40" width="10.5555555555556" customWidth="1"/>
-    <col min="41" max="41" width="10" customWidth="1"/>
-    <col min="43" max="43" width="6.33333333333333" customWidth="1"/>
-    <col min="44" max="44" width="14.5555555555556" customWidth="1"/>
-    <col min="45" max="45" width="6.88888888888889" customWidth="1"/>
-    <col min="46" max="46" width="5.77777777777778" customWidth="1"/>
-    <col min="47" max="47" width="7.88888888888889" customWidth="1"/>
-    <col min="48" max="48" width="32.3333333333333" customWidth="1"/>
-    <col min="49" max="49" width="8.44444444444444" customWidth="1"/>
-    <col min="50" max="52" width="12.1111111111111" customWidth="1"/>
-    <col min="53" max="53" width="13.6666666666667" customWidth="1"/>
-    <col min="54" max="54" width="15.3333333333333" customWidth="1"/>
-    <col min="55" max="55" width="21.3333333333333" customWidth="1"/>
-    <col min="56" max="56" width="12.4444444444444" customWidth="1"/>
-    <col min="57" max="57" width="15.8888888888889" customWidth="1"/>
-    <col min="58" max="58" width="21.4444444444444" customWidth="1"/>
-    <col min="59" max="59" width="18.6666666666667" customWidth="1"/>
-    <col min="60" max="60" width="18.3333333333333" customWidth="1"/>
-    <col min="61" max="61" width="19.1111111111111" customWidth="1"/>
-    <col min="62" max="62" width="7.22222222222222" customWidth="1"/>
-    <col min="63" max="63" width="7.77777777777778" customWidth="1"/>
-    <col min="64" max="64" width="12.6666666666667" customWidth="1"/>
-    <col min="65" max="65" width="10.1111111111111" customWidth="1"/>
-    <col min="66" max="66" width="11.8888888888889" customWidth="1"/>
-    <col min="67" max="67" width="7.66666666666667" customWidth="1"/>
-    <col min="68" max="68" width="10.3333333333333" customWidth="1"/>
-    <col min="69" max="69" width="10.1111111111111" customWidth="1"/>
-    <col min="70" max="70" width="12" customWidth="1"/>
-    <col min="71" max="71" width="12.1111111111111" customWidth="1"/>
-    <col min="72" max="72" width="8.66666666666667" customWidth="1"/>
-    <col min="73" max="73" width="10.1111111111111" customWidth="1"/>
-    <col min="74" max="74" width="9.22222222222222" customWidth="1"/>
-    <col min="75" max="75" width="12.1111111111111" customWidth="1"/>
-    <col min="76" max="76" width="13.5555555555556" customWidth="1"/>
-    <col min="77" max="77" width="10.1111111111111" customWidth="1"/>
-    <col min="78" max="79" width="23.1111111111111" customWidth="1"/>
-    <col min="80" max="80" width="7.44444444444444" customWidth="1"/>
-    <col min="81" max="81" width="10.3333333333333" customWidth="1"/>
-    <col min="82" max="82" width="8.55555555555556" customWidth="1"/>
-    <col min="83" max="83" width="9.66666666666667" customWidth="1"/>
-    <col min="84" max="84" width="13.6666666666667" customWidth="1"/>
-    <col min="85" max="85" width="11.1111111111111" customWidth="1"/>
-    <col min="86" max="86" width="14.6666666666667" customWidth="1"/>
-    <col min="87" max="87" width="28.4444444444444" customWidth="1"/>
-    <col min="88" max="88" width="25.6666666666667" customWidth="1"/>
-    <col min="89" max="89" width="14.6666666666667" customWidth="1"/>
-    <col min="90" max="90" width="32.1111111111111" customWidth="1"/>
-    <col min="91" max="91" width="35.3333333333333" customWidth="1"/>
-    <col min="92" max="103" width="14.6666666666667" customWidth="1"/>
-    <col min="104" max="104" width="9.22222222222222" customWidth="1"/>
-    <col min="105" max="105" width="6.22222222222222" customWidth="1"/>
-    <col min="106" max="119" width="14.6666666666667" customWidth="1"/>
-    <col min="120" max="120" width="27" customWidth="1"/>
+    <col min="1" max="1" width="8.55555555555556" style="6" customWidth="1"/>
+    <col min="2" max="2" width="8.77777777777778" style="6" customWidth="1"/>
+    <col min="3" max="3" width="12.8888888888889" style="6" customWidth="1"/>
+    <col min="4" max="5" width="6.77777777777778" style="6" customWidth="1"/>
+    <col min="6" max="6" width="15.2222222222222" style="6" customWidth="1"/>
+    <col min="7" max="7" width="20.7777777777778" style="6" customWidth="1"/>
+    <col min="8" max="8" width="18.5555555555556" style="6" customWidth="1"/>
+    <col min="9" max="9" width="15.2222222222222" style="6" customWidth="1"/>
+    <col min="10" max="10" width="14.1111111111111" style="6" customWidth="1"/>
+    <col min="11" max="12" width="9.66666666666667" style="6" customWidth="1"/>
+    <col min="13" max="13" width="8.77777777777778" style="6" customWidth="1"/>
+    <col min="14" max="14" width="16.3333333333333" style="6" customWidth="1"/>
+    <col min="15" max="15" width="9.66666666666667" style="6" customWidth="1"/>
+    <col min="16" max="16" width="10.7777777777778" style="6" customWidth="1"/>
+    <col min="17" max="17" width="13" style="6" customWidth="1"/>
+    <col min="18" max="18" width="6.77777777777778" style="6" customWidth="1"/>
+    <col min="19" max="20" width="6.66666666666667" style="6" customWidth="1"/>
+    <col min="21" max="21" width="11.8888888888889" style="6" customWidth="1"/>
+    <col min="22" max="22" width="7.44444444444444" style="6" customWidth="1"/>
+    <col min="23" max="24" width="10.7777777777778" style="6" customWidth="1"/>
+    <col min="25" max="25" width="13" style="6" customWidth="1"/>
+    <col min="26" max="26" width="8.55555555555556" style="6" customWidth="1"/>
+    <col min="27" max="27" width="6.66666666666667" style="6" customWidth="1"/>
+    <col min="28" max="28" width="10.7777777777778" style="6" customWidth="1"/>
+    <col min="29" max="29" width="6.33333333333333" style="6" customWidth="1"/>
+    <col min="30" max="30" width="10.7777777777778" style="6" customWidth="1"/>
+    <col min="31" max="31" width="6.33333333333333" style="6" customWidth="1"/>
+    <col min="32" max="32" width="8.55555555555556" style="6" customWidth="1"/>
+    <col min="33" max="33" width="10.7777777777778" style="6" customWidth="1"/>
+    <col min="34" max="34" width="9.66666666666667" style="6" customWidth="1"/>
+    <col min="35" max="35" width="10.7777777777778" style="6" customWidth="1"/>
+    <col min="36" max="36" width="8.55555555555556" style="6" customWidth="1"/>
+    <col min="37" max="37" width="15.2222222222222" style="6" customWidth="1"/>
+    <col min="38" max="39" width="7.44444444444444" style="6" customWidth="1"/>
+    <col min="40" max="41" width="9.77777777777778" style="6" customWidth="1"/>
+    <col min="42" max="42" width="6.77777777777778" style="6" customWidth="1"/>
+    <col min="43" max="43" width="6.33333333333333" style="6" customWidth="1"/>
+    <col min="44" max="44" width="10.7777777777778" style="6" customWidth="1"/>
+    <col min="45" max="45" width="6.33333333333333" style="6" customWidth="1"/>
+    <col min="46" max="46" width="5.66666666666667" style="6" customWidth="1"/>
+    <col min="47" max="47" width="7.44444444444444" style="6" customWidth="1"/>
+    <col min="48" max="48" width="25.2222222222222" style="6" customWidth="1"/>
+    <col min="49" max="49" width="7.77777777777778" style="6" customWidth="1"/>
+    <col min="50" max="50" width="11.8888888888889" style="6" customWidth="1"/>
+    <col min="51" max="51" width="11.7777777777778" style="6" customWidth="1"/>
+    <col min="52" max="52" width="9.77777777777778" style="6" customWidth="1"/>
+    <col min="53" max="53" width="13" style="6" customWidth="1"/>
+    <col min="54" max="54" width="12.8888888888889" style="6" customWidth="1"/>
+    <col min="55" max="55" width="17.7777777777778" style="6" customWidth="1"/>
+    <col min="56" max="56" width="8.55555555555556" style="6" customWidth="1"/>
+    <col min="57" max="57" width="14.7777777777778" style="6" customWidth="1"/>
+    <col min="58" max="58" width="17.4444444444444" style="6" customWidth="1"/>
+    <col min="59" max="59" width="17.7777777777778" style="6" customWidth="1"/>
+    <col min="60" max="60" width="14.7777777777778" style="6" customWidth="1"/>
+    <col min="61" max="61" width="15.2222222222222" style="6" customWidth="1"/>
+    <col min="62" max="62" width="6.33333333333333" style="6" customWidth="1"/>
+    <col min="63" max="63" width="7.44444444444444" style="6" customWidth="1"/>
+    <col min="64" max="64" width="10.7777777777778" style="6" customWidth="1"/>
+    <col min="65" max="65" width="9.66666666666667" style="6" customWidth="1"/>
+    <col min="66" max="66" width="11.8888888888889" style="6" customWidth="1"/>
+    <col min="67" max="67" width="7.44444444444444" style="6" customWidth="1"/>
+    <col min="68" max="69" width="9.66666666666667" style="6" customWidth="1"/>
+    <col min="70" max="70" width="10.6666666666667" style="6" customWidth="1"/>
+    <col min="71" max="71" width="11.7777777777778" style="6" customWidth="1"/>
+    <col min="72" max="72" width="8.55555555555556" style="6" customWidth="1"/>
+    <col min="73" max="73" width="9.77777777777778" style="6" customWidth="1"/>
+    <col min="74" max="74" width="8.55555555555556" style="6" customWidth="1"/>
+    <col min="75" max="75" width="9.66666666666667" style="6" customWidth="1"/>
+    <col min="76" max="76" width="25.2222222222222" style="6" customWidth="1"/>
+    <col min="77" max="77" width="13" style="6" customWidth="1"/>
+    <col min="78" max="78" width="43" style="6" customWidth="1"/>
+    <col min="79" max="79" width="20.7777777777778" style="6" customWidth="1"/>
+    <col min="80" max="80" width="7.44444444444444" style="6" customWidth="1"/>
+    <col min="81" max="81" width="9.66666666666667" style="6" customWidth="1"/>
+    <col min="82" max="82" width="8.55555555555556" style="6" customWidth="1"/>
+    <col min="83" max="83" width="9.66666666666667" style="6" customWidth="1"/>
+    <col min="84" max="84" width="8.55555555555556" style="6" customWidth="1"/>
+    <col min="85" max="85" width="10.7777777777778" style="6" customWidth="1"/>
+    <col min="86" max="86" width="13.7777777777778" style="6" customWidth="1"/>
+    <col min="87" max="87" width="27.7777777777778" style="6" customWidth="1"/>
+    <col min="88" max="88" width="23" style="6" customWidth="1"/>
+    <col min="89" max="89" width="11.8888888888889" style="6" customWidth="1"/>
+    <col min="90" max="90" width="27.7777777777778" style="6" customWidth="1"/>
+    <col min="91" max="91" width="21.7777777777778" style="6" customWidth="1"/>
+    <col min="92" max="92" width="13.7777777777778" style="6" customWidth="1"/>
+    <col min="93" max="93" width="13" style="6" customWidth="1"/>
+    <col min="94" max="95" width="14.1111111111111" style="6" customWidth="1"/>
+    <col min="96" max="96" width="11.8888888888889" style="6" customWidth="1"/>
+    <col min="97" max="97" width="10.7777777777778" style="6" customWidth="1"/>
+    <col min="98" max="98" width="14.1111111111111" style="6" customWidth="1"/>
+    <col min="99" max="99" width="10.7777777777778" style="6" customWidth="1"/>
+    <col min="100" max="101" width="11.8888888888889" style="6" customWidth="1"/>
+    <col min="102" max="102" width="9.77777777777778" style="6" customWidth="1"/>
+    <col min="103" max="103" width="10.7777777777778" style="6" customWidth="1"/>
+    <col min="104" max="104" width="8.55555555555556" style="6" customWidth="1"/>
+    <col min="105" max="105" width="6.66666666666667" style="6" customWidth="1"/>
+    <col min="106" max="106" width="8.55555555555556" style="6" customWidth="1"/>
+    <col min="107" max="107" width="14.1111111111111" style="6" customWidth="1"/>
+    <col min="108" max="108" width="12.7777777777778" style="6" customWidth="1"/>
+    <col min="109" max="109" width="13" style="6" customWidth="1"/>
+    <col min="110" max="112" width="11.8888888888889" style="6" customWidth="1"/>
+    <col min="113" max="113" width="9.77777777777778" style="6" customWidth="1"/>
+    <col min="114" max="114" width="9.66666666666667" style="6" customWidth="1"/>
+    <col min="115" max="115" width="14.1111111111111" style="6" customWidth="1"/>
+    <col min="116" max="116" width="11.7777777777778" style="6" customWidth="1"/>
+    <col min="117" max="117" width="13.7777777777778" style="6" customWidth="1"/>
+    <col min="118" max="120" width="11.8888888888889" style="6" customWidth="1"/>
+    <col min="121" max="121" width="24.7777777777778" style="6" customWidth="1"/>
+    <col min="122" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="70" customHeight="1" spans="1:120">
-      <c r="A1" s="6" t="s">
+    <row r="1" s="1" customFormat="1" ht="70" customHeight="1" spans="1:121">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="7" t="s">
@@ -2269,69 +2310,76 @@
       <c r="DP1" s="7" t="s">
         <v>116</v>
       </c>
+      <c r="DQ1" s="7" t="s">
+        <v>117</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="72" spans="1:119">
+    <row r="2" s="2" customFormat="1" ht="84" spans="1:120">
       <c r="A2" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C2" s="9">
         <v>86695778963</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J2" s="9"/>
       <c r="K2" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
+      <c r="P2" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>129</v>
+      </c>
       <c r="R2" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="S2" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="T2" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="U2" s="9" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="V2" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="W2" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="X2" s="9" t="s">
         <v>130</v>
+      </c>
+      <c r="X2" s="9">
+        <v>800</v>
       </c>
       <c r="Y2" s="8">
         <v>5</v>
@@ -2340,7 +2388,7 @@
         <v>30</v>
       </c>
       <c r="AA2" s="12" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="AB2" s="12"/>
       <c r="AC2" s="12"/>
@@ -2351,199 +2399,215 @@
       <c r="AH2" s="12"/>
       <c r="AI2" s="12"/>
       <c r="AJ2" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AK2" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="AL2" s="9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AM2" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="AN2" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="AO2" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="AP2" s="9" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AQ2" s="9" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="AR2" s="9" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="AS2" s="9"/>
       <c r="AT2" s="9"/>
       <c r="AU2" s="9"/>
       <c r="AV2" s="9"/>
-      <c r="AW2" s="9"/>
-      <c r="AX2" s="9"/>
-      <c r="AY2" s="9"/>
-      <c r="AZ2" s="9"/>
-      <c r="BA2" s="9"/>
-      <c r="BB2" s="9"/>
+      <c r="AW2" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX2" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AY2" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="AZ2" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="BA2" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="BB2" s="9">
+        <v>86695778963</v>
+      </c>
       <c r="BC2" s="9"/>
       <c r="BD2" s="9"/>
       <c r="BE2" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BF2" s="9" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="BG2" s="9" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="BH2" s="9" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="BI2" s="9" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="BJ2" s="9" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="BK2" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="BL2" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="BM2" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="BN2" s="14" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="BO2" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="BP2" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="BQ2" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="BR2" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="BS2" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="BT2" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="BU2" s="9" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="BV2" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="BW2" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="BX2" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="BY2" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="BZ2" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="CA2" s="9"/>
       <c r="CB2" s="9" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="CC2" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="CD2" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="CE2" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="CF2" s="9"/>
       <c r="CG2" s="9"/>
       <c r="CH2" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="CI2" s="2" t="s">
-        <v>139</v>
+        <v>130</v>
+      </c>
+      <c r="CI2" s="9" t="s">
+        <v>151</v>
       </c>
       <c r="CJ2" s="9"/>
       <c r="CK2" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="DO2" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="DN2" s="8"/>
+      <c r="DO2" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="DP2" s="8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" s="3" customFormat="1" ht="84" spans="1:121">
+      <c r="A3" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="C3" s="9">
+        <v>86695778963</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G3" s="9" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="3" s="3" customFormat="1" ht="84" spans="1:120">
-      <c r="A3" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="C3" s="9">
-        <v>39008846636</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>122</v>
-      </c>
       <c r="H3" s="8"/>
-      <c r="I3" s="8" t="s">
-        <v>144</v>
+      <c r="I3" s="9" t="s">
+        <v>124</v>
       </c>
       <c r="J3" s="8"/>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="L3" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>146</v>
+      <c r="L3" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>154</v>
       </c>
       <c r="O3" s="8"/>
       <c r="P3" s="8" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="R3" s="8"/>
       <c r="S3" s="8"/>
       <c r="T3" s="8"/>
-      <c r="U3" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="V3" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="W3" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="X3" s="8" t="s">
-        <v>150</v>
+      <c r="U3" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="V3" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="W3" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="X3" s="9">
+        <v>800</v>
       </c>
       <c r="Y3" s="8">
         <v>5</v>
@@ -2560,286 +2624,291 @@
       <c r="AG3" s="8"/>
       <c r="AH3" s="8"/>
       <c r="AI3" s="8"/>
-      <c r="AJ3" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="AK3" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="AL3" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="AM3" s="8"/>
-      <c r="AN3" s="8"/>
-      <c r="AO3" s="8"/>
-      <c r="AP3" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="AQ3" s="8" t="s">
+      <c r="AJ3" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="AK3" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="AL3" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="AM3" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="AN3" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="AO3" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="AP3" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="AQ3" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="AR3" s="9" t="s">
         <v>155</v>
-      </c>
-      <c r="AR3" s="8" t="s">
-        <v>156</v>
       </c>
       <c r="AS3" s="8"/>
       <c r="AT3" s="8"/>
       <c r="AU3" s="8"/>
       <c r="AV3" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="AW3" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="AX3" s="8" t="s">
-        <v>158</v>
+        <v>126</v>
+      </c>
+      <c r="AW3" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX3" s="9" t="s">
+        <v>139</v>
       </c>
       <c r="AY3" s="8" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="AZ3" s="8" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="BA3" s="8" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="BB3" s="9">
         <v>39008846636</v>
       </c>
       <c r="BC3" s="9" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="BD3" s="8"/>
       <c r="BE3" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="BF3" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="BG3" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="BH3" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="BI3" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="BJ3" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="BK3" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="BL3" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="BM3" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="BF3" s="9" t="s">
+      <c r="BN3" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="BO3" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="BG3" s="9" t="s">
+      <c r="BP3" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="BH3" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="BI3" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="BJ3" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="BK3" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="BL3" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="BM3" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="BN3" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="BO3" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="BP3" s="9" t="s">
-        <v>172</v>
-      </c>
       <c r="BQ3" s="9" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="BR3" s="9">
         <v>411203205</v>
       </c>
       <c r="BS3" s="9" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="BT3" s="9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="BU3" s="9" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="BV3" s="9" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="BW3" s="9">
         <v>13501975</v>
       </c>
-      <c r="BX3" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="BY3" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="BZ3" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="CA3" s="8"/>
+      <c r="BX3" s="8"/>
+      <c r="BY3" s="8"/>
+      <c r="BZ3" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="CA3" s="13" t="s">
+        <v>169</v>
+      </c>
       <c r="CB3" s="8" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="CC3" s="8" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="CD3" s="8" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="CE3" s="8" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="CF3" s="8"/>
       <c r="CG3" s="8"/>
       <c r="CH3" s="8" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="CI3" s="8"/>
       <c r="CJ3" s="8"/>
       <c r="CK3" s="8"/>
       <c r="CL3" s="8" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="CM3" s="8" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="CN3" s="8" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="CO3" s="8"/>
       <c r="CP3" s="8"/>
       <c r="CQ3" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="CR3" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="CS3" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="CT3" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="CU3" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="CV3" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="CW3" s="17"/>
+      <c r="CX3" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="CY3" s="17"/>
+      <c r="CZ3" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="DA3" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="DB3" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="CR3" s="8" t="s">
+      <c r="DC3" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="CS3" s="8" t="s">
+      <c r="DD3" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="CT3" s="18" t="s">
+      <c r="DE3" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="CU3" s="18" t="s">
+      <c r="DF3" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="CV3" s="18" t="s">
+      <c r="DG3" s="17"/>
+      <c r="DH3" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="CW3" s="18"/>
-      <c r="CX3" s="18" t="s">
+      <c r="DI3" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="CY3" s="18"/>
-      <c r="CZ3" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="DA3" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="DB3" s="18" t="s">
+      <c r="DJ3" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="DC3" s="18" t="s">
+      <c r="DK3" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="DL3" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="DD3" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="DE3" s="18" t="s">
+      <c r="DM3" s="17"/>
+      <c r="DN3" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="DF3" s="18" t="s">
+      <c r="DO3" s="17"/>
+      <c r="DP3" s="17"/>
+      <c r="DQ3" s="8"/>
+    </row>
+    <row r="4" s="2" customFormat="1" ht="72" spans="1:95">
+      <c r="A4" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="DG3" s="18"/>
-      <c r="DH3" s="18" t="s">
+      <c r="B4" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="DI3" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="DJ3" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="DK3" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="DL3" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="DM3" s="18"/>
-      <c r="DN3" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="DO3" s="18"/>
-      <c r="DP3" s="8" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" ht="72" spans="1:89">
-      <c r="A4" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>141</v>
       </c>
       <c r="C4" s="9">
         <v>39008846636</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>142</v>
+        <v>196</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>143</v>
+        <v>186</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H4" s="9"/>
       <c r="I4" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J4" s="9"/>
       <c r="K4" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>146</v>
+        <v>197</v>
       </c>
       <c r="O4" s="9"/>
-      <c r="P4" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q4" s="9"/>
+      <c r="P4" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>129</v>
+      </c>
       <c r="R4" s="9" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="S4" s="9" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="T4" s="9">
         <v>10000</v>
       </c>
       <c r="U4" s="9" t="s">
-        <v>148</v>
+        <v>200</v>
       </c>
       <c r="V4" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="W4" s="8" t="s">
-        <v>149</v>
+        <v>132</v>
+      </c>
+      <c r="W4" s="9">
+        <v>100</v>
       </c>
       <c r="X4" s="9" t="s">
-        <v>150</v>
+        <v>201</v>
       </c>
       <c r="Y4" s="8">
         <v>5</v>
@@ -2848,7 +2917,7 @@
         <v>30</v>
       </c>
       <c r="AA4" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="AB4" s="9"/>
       <c r="AC4" s="9"/>
@@ -2859,109 +2928,109 @@
       <c r="AH4" s="9"/>
       <c r="AI4" s="9"/>
       <c r="AJ4" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="AK4" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="AL4" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="AM4" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="AK4" s="9" t="s">
+      <c r="AN4" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="AL4" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="AM4" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="AN4" s="9" t="s">
-        <v>207</v>
-      </c>
       <c r="AO4" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AP4" s="9" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AQ4" s="9" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="AR4" s="9" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="AS4" s="9"/>
       <c r="AT4" s="9"/>
       <c r="AU4" s="9"/>
       <c r="AV4" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="AW4" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX4" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="AW4" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="AX4" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="AY4" s="9"/>
       <c r="AZ4" s="9"/>
-      <c r="BA4" s="9" t="s">
-        <v>161</v>
+      <c r="BA4" s="8" t="s">
+        <v>142</v>
       </c>
       <c r="BB4" s="9">
         <v>39008846636</v>
       </c>
       <c r="BC4" s="9" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="BD4" s="9"/>
       <c r="BE4" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="BF4" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="BG4" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="BH4" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="BI4" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="BJ4" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="BK4" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="BL4" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="BM4" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="BF4" s="9" t="s">
+      <c r="BN4" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="BO4" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="BG4" s="9" t="s">
+      <c r="BP4" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="BH4" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="BI4" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="BJ4" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="BK4" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="BL4" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="BM4" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="BN4" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="BO4" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="BP4" s="9" t="s">
-        <v>172</v>
-      </c>
       <c r="BQ4" s="9" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="BR4" s="9">
         <v>411203205</v>
       </c>
       <c r="BS4" s="9" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="BT4" s="9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="BU4" s="9" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="BV4" s="9" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="BW4" s="9">
         <v>13501975</v>
@@ -2969,100 +3038,118 @@
       <c r="BX4" s="9"/>
       <c r="BY4" s="9"/>
       <c r="BZ4" s="13" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="CA4" s="13" t="s">
-        <v>210</v>
+        <v>169</v>
       </c>
       <c r="CB4" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="CC4" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="CD4" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="CE4" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="CF4" s="9"/>
       <c r="CG4" s="9"/>
       <c r="CH4" s="9" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="CI4" s="9" t="s">
-        <v>211</v>
+        <v>151</v>
       </c>
       <c r="CJ4" s="9"/>
       <c r="CK4" s="2" t="s">
-        <v>139</v>
+        <v>152</v>
+      </c>
+      <c r="CL4" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="CM4" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="CN4" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="CO4" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="CP4" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="CQ4" s="6" t="s">
+        <v>210</v>
       </c>
     </row>
-    <row r="5" s="4" customFormat="1" ht="129" customHeight="1" spans="1:120">
+    <row r="5" s="4" customFormat="1" ht="129" customHeight="1" spans="1:121">
       <c r="A5" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>141</v>
+        <v>195</v>
       </c>
       <c r="C5" s="9">
         <v>39008846636</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>142</v>
+        <v>196</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>143</v>
+        <v>186</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>213</v>
+        <v>123</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9" t="s">
-        <v>144</v>
+        <v>212</v>
       </c>
       <c r="J5" s="9"/>
       <c r="K5" s="9" t="s">
-        <v>214</v>
+        <v>125</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>145</v>
+        <v>130</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>213</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>146</v>
+        <v>197</v>
       </c>
       <c r="O5" s="9"/>
       <c r="P5" s="8" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="Q5" s="9"/>
       <c r="R5" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="S5" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="T5" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="U5" s="9" t="s">
-        <v>148</v>
+        <v>200</v>
       </c>
       <c r="V5" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="W5" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="X5" s="9" t="s">
-        <v>150</v>
+        <v>132</v>
+      </c>
+      <c r="W5" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="X5" s="9">
+        <v>800</v>
       </c>
       <c r="Y5" s="8">
         <v>5</v>
@@ -3071,7 +3158,7 @@
         <v>30</v>
       </c>
       <c r="AA5" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="AB5" s="13"/>
       <c r="AC5" s="13"/>
@@ -3082,43 +3169,43 @@
       <c r="AH5" s="13"/>
       <c r="AI5" s="13"/>
       <c r="AJ5" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="AK5" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="AL5" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="AM5" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="AK5" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="AL5" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="AM5" s="9" t="s">
-        <v>124</v>
-      </c>
       <c r="AN5" s="9" t="s">
-        <v>124</v>
+        <v>216</v>
       </c>
       <c r="AO5" s="9" t="s">
-        <v>124</v>
+        <v>216</v>
       </c>
       <c r="AP5" s="9" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="AQ5" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="AR5" s="9" t="s">
         <v>155</v>
-      </c>
-      <c r="AR5" s="9" t="s">
-        <v>215</v>
       </c>
       <c r="AS5" s="9"/>
       <c r="AT5" s="9"/>
       <c r="AU5" s="9"/>
       <c r="AV5" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AW5" s="9" t="s">
-        <v>208</v>
+        <v>138</v>
       </c>
       <c r="AX5" s="9" t="s">
-        <v>209</v>
+        <v>139</v>
       </c>
       <c r="AY5" s="9"/>
       <c r="AZ5" s="9"/>
@@ -3127,62 +3214,62 @@
         <v>39008846636</v>
       </c>
       <c r="BC5" s="9" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="BD5" s="9"/>
       <c r="BE5" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="BF5" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="BG5" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="BH5" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="BI5" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="BJ5" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="BK5" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="BL5" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="BM5" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="BF5" s="9" t="s">
+      <c r="BN5" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="BO5" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="BG5" s="9" t="s">
+      <c r="BP5" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="BH5" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="BI5" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="BJ5" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="BK5" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="BL5" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="BM5" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="BN5" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="BO5" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="BP5" s="9" t="s">
-        <v>172</v>
-      </c>
       <c r="BQ5" s="9" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="BR5" s="9">
         <v>411203205</v>
       </c>
       <c r="BS5" s="9" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="BT5" s="9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="BU5" s="9" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="BV5" s="9" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="BW5" s="9">
         <v>13501975</v>
@@ -3190,114 +3277,115 @@
       <c r="BX5" s="9"/>
       <c r="BY5" s="9"/>
       <c r="BZ5" s="13" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="CA5" s="13" t="s">
-        <v>210</v>
+        <v>169</v>
       </c>
       <c r="CB5" s="13" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="CC5" s="13" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="CD5" s="13" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="CE5" s="13" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="CF5" s="13"/>
       <c r="CG5" s="13"/>
       <c r="CH5" s="13" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="CI5" s="13"/>
       <c r="CJ5" s="13"/>
       <c r="CK5" s="8"/>
       <c r="CL5" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="CM5" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="CN5" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="CO5" s="8"/>
       <c r="CP5" s="8"/>
       <c r="CQ5" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="CR5" s="8" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="CS5" s="8"/>
-      <c r="CT5" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="CU5" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="CV5" s="18" t="s">
-        <v>220</v>
-      </c>
-      <c r="CW5" s="18" t="s">
+      <c r="CT5" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="CU5" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="CV5" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="CX5" s="18" t="s">
+      <c r="CW5" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="CY5" s="18" t="s">
+      <c r="CX5" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="CZ5" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="DA5" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="DB5" s="18" t="s">
+      <c r="CY5" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="CZ5" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="DA5" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="DB5" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="DC5" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="DD5" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="DE5" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="DF5" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="DG5" s="17" t="s">
+        <v>228</v>
+      </c>
+      <c r="DH5" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="DI5" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="DJ5" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="DC5" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="DD5" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="DE5" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="DF5" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="DG5" s="18" t="s">
-        <v>224</v>
-      </c>
-      <c r="DH5" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="DI5" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="DJ5" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="DK5" s="18"/>
-      <c r="DL5" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="DM5" s="18" t="s">
-        <v>226</v>
-      </c>
-      <c r="DN5" s="18"/>
-      <c r="DO5" s="18"/>
-      <c r="DP5" s="8" t="s">
-        <v>200</v>
+      <c r="DK5" s="17"/>
+      <c r="DL5" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="DM5" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="DN5" s="17"/>
+      <c r="DO5" s="17"/>
+      <c r="DP5" s="17"/>
+      <c r="DQ5" s="8" t="s">
+        <v>231</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" spans="1:120">
+    <row r="6" s="3" customFormat="1" spans="1:121">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -3363,11 +3451,11 @@
       <c r="BK6" s="8"/>
       <c r="BL6" s="8"/>
       <c r="BM6" s="8"/>
-      <c r="BN6" s="16"/>
+      <c r="BN6" s="15"/>
       <c r="BO6" s="8"/>
       <c r="BP6" s="8"/>
       <c r="BQ6" s="8"/>
-      <c r="BR6" s="17"/>
+      <c r="BR6" s="16"/>
       <c r="BS6" s="8"/>
       <c r="BT6" s="8"/>
       <c r="BU6" s="13"/>
@@ -3395,275 +3483,278 @@
       <c r="CQ6" s="8"/>
       <c r="CR6" s="8"/>
       <c r="CS6" s="8"/>
-      <c r="CT6" s="18"/>
-      <c r="CU6" s="18"/>
-      <c r="CV6" s="18"/>
-      <c r="CW6" s="18"/>
-      <c r="CX6" s="18"/>
-      <c r="CY6" s="18"/>
-      <c r="CZ6" s="18"/>
-      <c r="DA6" s="18"/>
-      <c r="DB6" s="18"/>
-      <c r="DC6" s="18"/>
-      <c r="DD6" s="18"/>
-      <c r="DE6" s="18"/>
-      <c r="DF6" s="18"/>
-      <c r="DG6" s="18"/>
-      <c r="DH6" s="18"/>
-      <c r="DI6" s="18"/>
-      <c r="DJ6" s="18"/>
-      <c r="DK6" s="18"/>
-      <c r="DL6" s="18"/>
-      <c r="DM6" s="18"/>
-      <c r="DN6" s="18"/>
-      <c r="DO6" s="18"/>
+      <c r="CT6" s="8"/>
+      <c r="CU6" s="8"/>
+      <c r="CV6" s="8"/>
+      <c r="CW6" s="8"/>
+      <c r="CX6" s="8"/>
+      <c r="CY6" s="8"/>
+      <c r="CZ6" s="8"/>
+      <c r="DA6" s="8"/>
+      <c r="DB6" s="8"/>
+      <c r="DC6" s="8"/>
+      <c r="DD6" s="8"/>
+      <c r="DE6" s="8"/>
+      <c r="DF6" s="8"/>
+      <c r="DG6" s="8"/>
+      <c r="DH6" s="8"/>
+      <c r="DI6" s="8"/>
+      <c r="DJ6" s="8"/>
+      <c r="DK6" s="8"/>
+      <c r="DL6" s="8"/>
+      <c r="DM6" s="8"/>
+      <c r="DN6" s="8"/>
+      <c r="DO6" s="8"/>
       <c r="DP6" s="8"/>
+      <c r="DQ6" s="8"/>
     </row>
-    <row r="7" s="3" customFormat="1" spans="1:120">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="8"/>
-      <c r="W7" s="8"/>
-      <c r="X7" s="8"/>
-      <c r="Y7" s="8"/>
-      <c r="Z7" s="8"/>
-      <c r="AA7" s="8"/>
-      <c r="AB7" s="8"/>
-      <c r="AC7" s="8"/>
-      <c r="AD7" s="8"/>
-      <c r="AE7" s="8"/>
-      <c r="AF7" s="8"/>
-      <c r="AG7" s="8"/>
-      <c r="AH7" s="8"/>
-      <c r="AI7" s="8"/>
-      <c r="AJ7" s="8"/>
-      <c r="AK7" s="8"/>
-      <c r="AL7" s="8"/>
-      <c r="AM7" s="8"/>
-      <c r="AN7" s="8"/>
-      <c r="AO7" s="8"/>
-      <c r="AP7" s="8"/>
-      <c r="AQ7" s="8"/>
-      <c r="AR7" s="8"/>
-      <c r="AS7" s="8"/>
-      <c r="AT7" s="8"/>
-      <c r="AU7" s="8"/>
-      <c r="AV7" s="8"/>
-      <c r="AW7" s="8"/>
-      <c r="AX7" s="8"/>
-      <c r="AY7" s="8"/>
-      <c r="AZ7" s="8"/>
-      <c r="BA7" s="8"/>
-      <c r="BB7" s="8"/>
-      <c r="BC7" s="8"/>
-      <c r="BD7" s="8"/>
-      <c r="BE7" s="8"/>
-      <c r="BF7" s="8"/>
-      <c r="BG7" s="8"/>
-      <c r="BH7" s="8"/>
-      <c r="BI7" s="8"/>
-      <c r="BJ7" s="8"/>
-      <c r="BK7" s="8"/>
-      <c r="BL7" s="8"/>
-      <c r="BM7" s="8"/>
-      <c r="BN7" s="16"/>
-      <c r="BO7" s="8"/>
-      <c r="BP7" s="8"/>
-      <c r="BQ7" s="8"/>
-      <c r="BR7" s="17"/>
-      <c r="BS7" s="8"/>
-      <c r="BT7" s="8"/>
-      <c r="BU7" s="13"/>
-      <c r="BV7" s="8"/>
-      <c r="BW7" s="8"/>
-      <c r="BX7" s="8"/>
-      <c r="BY7" s="8"/>
-      <c r="BZ7" s="8"/>
-      <c r="CA7" s="8"/>
-      <c r="CB7" s="8"/>
-      <c r="CC7" s="8"/>
-      <c r="CD7" s="8"/>
-      <c r="CE7" s="8"/>
-      <c r="CF7" s="8"/>
-      <c r="CG7" s="8"/>
-      <c r="CH7" s="8"/>
-      <c r="CI7" s="8"/>
-      <c r="CJ7" s="8"/>
-      <c r="CK7" s="8"/>
-      <c r="CL7" s="8"/>
-      <c r="CM7" s="8"/>
-      <c r="CN7" s="8"/>
-      <c r="CO7" s="8"/>
-      <c r="CP7" s="8"/>
-      <c r="CQ7" s="8"/>
-      <c r="CR7" s="8"/>
-      <c r="CS7" s="8"/>
-      <c r="CT7" s="8"/>
-      <c r="CU7" s="8"/>
-      <c r="CV7" s="8"/>
-      <c r="CW7" s="8"/>
-      <c r="CX7" s="8"/>
-      <c r="CY7" s="8"/>
-      <c r="CZ7" s="8"/>
-      <c r="DA7" s="8"/>
-      <c r="DB7" s="8"/>
-      <c r="DC7" s="8"/>
-      <c r="DD7" s="8"/>
-      <c r="DE7" s="8"/>
-      <c r="DF7" s="8"/>
-      <c r="DG7" s="8"/>
-      <c r="DH7" s="8"/>
-      <c r="DI7" s="8"/>
-      <c r="DJ7" s="8"/>
-      <c r="DK7" s="8"/>
-      <c r="DL7" s="8"/>
-      <c r="DM7" s="8"/>
-      <c r="DN7" s="8"/>
-      <c r="DO7" s="8"/>
-      <c r="DP7" s="8"/>
+    <row r="7" s="5" customFormat="1" spans="1:121">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
+      <c r="S7" s="10"/>
+      <c r="T7" s="10"/>
+      <c r="U7" s="10"/>
+      <c r="V7" s="10"/>
+      <c r="W7" s="10"/>
+      <c r="X7" s="10"/>
+      <c r="Y7" s="10"/>
+      <c r="Z7" s="10"/>
+      <c r="AA7" s="10"/>
+      <c r="AB7" s="10"/>
+      <c r="AC7" s="10"/>
+      <c r="AD7" s="10"/>
+      <c r="AE7" s="10"/>
+      <c r="AF7" s="10"/>
+      <c r="AG7" s="10"/>
+      <c r="AH7" s="10"/>
+      <c r="AI7" s="10"/>
+      <c r="AJ7" s="10"/>
+      <c r="AK7" s="10"/>
+      <c r="AL7" s="10"/>
+      <c r="AM7" s="10"/>
+      <c r="AN7" s="10"/>
+      <c r="AO7" s="10"/>
+      <c r="AP7" s="10"/>
+      <c r="AQ7" s="10"/>
+      <c r="AR7" s="10"/>
+      <c r="AS7" s="10"/>
+      <c r="AT7" s="10"/>
+      <c r="AU7" s="10"/>
+      <c r="AV7" s="10"/>
+      <c r="AW7" s="10"/>
+      <c r="AX7" s="10"/>
+      <c r="AY7" s="10"/>
+      <c r="AZ7" s="10"/>
+      <c r="BA7" s="10"/>
+      <c r="BB7" s="10"/>
+      <c r="BC7" s="10"/>
+      <c r="BD7" s="10"/>
+      <c r="BE7" s="10"/>
+      <c r="BF7" s="10"/>
+      <c r="BG7" s="10"/>
+      <c r="BH7" s="10"/>
+      <c r="BI7" s="10"/>
+      <c r="BJ7" s="10"/>
+      <c r="BK7" s="10"/>
+      <c r="BL7" s="10"/>
+      <c r="BM7" s="10"/>
+      <c r="BN7" s="10"/>
+      <c r="BO7" s="10"/>
+      <c r="BP7" s="10"/>
+      <c r="BQ7" s="10"/>
+      <c r="BR7" s="10"/>
+      <c r="BS7" s="10"/>
+      <c r="BT7" s="10"/>
+      <c r="BU7" s="10"/>
+      <c r="BV7" s="10"/>
+      <c r="BW7" s="10"/>
+      <c r="BX7" s="10"/>
+      <c r="BY7" s="10"/>
+      <c r="BZ7" s="10"/>
+      <c r="CA7" s="10"/>
+      <c r="CB7" s="10"/>
+      <c r="CC7" s="10"/>
+      <c r="CD7" s="10"/>
+      <c r="CE7" s="10"/>
+      <c r="CF7" s="10"/>
+      <c r="CG7" s="10"/>
+      <c r="CH7" s="10"/>
+      <c r="CI7" s="10"/>
+      <c r="CJ7" s="10"/>
+      <c r="CK7" s="10"/>
+      <c r="CL7" s="10"/>
+      <c r="CM7" s="10"/>
+      <c r="CN7" s="10"/>
+      <c r="CO7" s="10"/>
+      <c r="CP7" s="10"/>
+      <c r="CQ7" s="10"/>
+      <c r="CR7" s="10"/>
+      <c r="CS7" s="10"/>
+      <c r="CT7" s="10"/>
+      <c r="CU7" s="10"/>
+      <c r="CV7" s="10"/>
+      <c r="CW7" s="10"/>
+      <c r="CX7" s="10"/>
+      <c r="CY7" s="10"/>
+      <c r="CZ7" s="10"/>
+      <c r="DA7" s="10"/>
+      <c r="DB7" s="10"/>
+      <c r="DC7" s="10"/>
+      <c r="DD7" s="10"/>
+      <c r="DE7" s="10"/>
+      <c r="DF7" s="10"/>
+      <c r="DG7" s="10"/>
+      <c r="DH7" s="10"/>
+      <c r="DI7" s="10"/>
+      <c r="DJ7" s="10"/>
+      <c r="DK7" s="10"/>
+      <c r="DL7" s="10"/>
+      <c r="DM7" s="10"/>
+      <c r="DN7" s="10"/>
+      <c r="DO7" s="10"/>
+      <c r="DP7" s="10"/>
+      <c r="DQ7" s="10"/>
     </row>
-    <row r="8" s="3" customFormat="1" spans="1:120">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
-      <c r="V8" s="8"/>
-      <c r="W8" s="8"/>
-      <c r="X8" s="8"/>
-      <c r="Y8" s="8"/>
-      <c r="Z8" s="8"/>
-      <c r="AA8" s="8"/>
-      <c r="AB8" s="8"/>
-      <c r="AC8" s="8"/>
-      <c r="AD8" s="8"/>
-      <c r="AE8" s="8"/>
-      <c r="AF8" s="8"/>
-      <c r="AG8" s="8"/>
-      <c r="AH8" s="8"/>
-      <c r="AI8" s="8"/>
-      <c r="AJ8" s="8"/>
-      <c r="AK8" s="8"/>
-      <c r="AL8" s="8"/>
-      <c r="AM8" s="8"/>
-      <c r="AN8" s="8"/>
-      <c r="AO8" s="8"/>
-      <c r="AP8" s="8"/>
-      <c r="AQ8" s="8"/>
-      <c r="AR8" s="8"/>
-      <c r="AS8" s="8"/>
-      <c r="AT8" s="8"/>
-      <c r="AU8" s="8"/>
-      <c r="AV8" s="8"/>
-      <c r="AW8" s="8"/>
-      <c r="AX8" s="8"/>
-      <c r="AY8" s="8"/>
-      <c r="AZ8" s="8"/>
-      <c r="BA8" s="8"/>
-      <c r="BB8" s="8"/>
-      <c r="BC8" s="8"/>
-      <c r="BD8" s="8"/>
-      <c r="BE8" s="8"/>
-      <c r="BF8" s="8"/>
-      <c r="BG8" s="8"/>
-      <c r="BH8" s="8"/>
-      <c r="BI8" s="8"/>
-      <c r="BJ8" s="8"/>
-      <c r="BK8" s="8"/>
-      <c r="BL8" s="8"/>
-      <c r="BM8" s="8"/>
-      <c r="BN8" s="16"/>
-      <c r="BO8" s="8"/>
-      <c r="BP8" s="8"/>
-      <c r="BQ8" s="8"/>
-      <c r="BR8" s="17"/>
-      <c r="BS8" s="8"/>
-      <c r="BT8" s="8"/>
-      <c r="BU8" s="13"/>
-      <c r="BV8" s="8"/>
-      <c r="BW8" s="8"/>
-      <c r="BX8" s="8"/>
-      <c r="BY8" s="8"/>
-      <c r="BZ8" s="8"/>
-      <c r="CA8" s="8"/>
-      <c r="CB8" s="8"/>
-      <c r="CC8" s="8"/>
-      <c r="CD8" s="8"/>
-      <c r="CE8" s="8"/>
-      <c r="CF8" s="8"/>
-      <c r="CG8" s="8"/>
-      <c r="CH8" s="8"/>
-      <c r="CI8" s="8"/>
-      <c r="CJ8" s="8"/>
-      <c r="CK8" s="8"/>
-      <c r="CL8" s="8"/>
-      <c r="CM8" s="8"/>
-      <c r="CN8" s="8"/>
-      <c r="CO8" s="8"/>
-      <c r="CP8" s="8"/>
-      <c r="CQ8" s="8"/>
-      <c r="CR8" s="8"/>
-      <c r="CS8" s="8"/>
-      <c r="CT8" s="8"/>
-      <c r="CU8" s="8"/>
-      <c r="CV8" s="8"/>
-      <c r="CW8" s="8"/>
-      <c r="CX8" s="8"/>
-      <c r="CY8" s="8"/>
-      <c r="CZ8" s="8"/>
-      <c r="DA8" s="8"/>
-      <c r="DB8" s="8"/>
-      <c r="DC8" s="8"/>
-      <c r="DD8" s="8"/>
-      <c r="DE8" s="8"/>
-      <c r="DF8" s="8"/>
-      <c r="DG8" s="8"/>
-      <c r="DH8" s="8"/>
-      <c r="DI8" s="8"/>
-      <c r="DJ8" s="8"/>
-      <c r="DK8" s="8"/>
-      <c r="DL8" s="8"/>
-      <c r="DM8" s="8"/>
-      <c r="DN8" s="8"/>
-      <c r="DO8" s="8"/>
-      <c r="DP8" s="8"/>
+    <row r="8" s="5" customFormat="1" spans="1:121">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="10"/>
+      <c r="T8" s="10"/>
+      <c r="U8" s="10"/>
+      <c r="V8" s="10"/>
+      <c r="W8" s="10"/>
+      <c r="X8" s="10"/>
+      <c r="Y8" s="10"/>
+      <c r="Z8" s="10"/>
+      <c r="AA8" s="10"/>
+      <c r="AB8" s="10"/>
+      <c r="AC8" s="10"/>
+      <c r="AD8" s="10"/>
+      <c r="AE8" s="10"/>
+      <c r="AF8" s="10"/>
+      <c r="AG8" s="10"/>
+      <c r="AH8" s="10"/>
+      <c r="AI8" s="10"/>
+      <c r="AJ8" s="10"/>
+      <c r="AK8" s="10"/>
+      <c r="AL8" s="10"/>
+      <c r="AM8" s="10"/>
+      <c r="AN8" s="10"/>
+      <c r="AO8" s="10"/>
+      <c r="AP8" s="10"/>
+      <c r="AQ8" s="10"/>
+      <c r="AR8" s="10"/>
+      <c r="AS8" s="10"/>
+      <c r="AT8" s="10"/>
+      <c r="AU8" s="10"/>
+      <c r="AV8" s="10"/>
+      <c r="AW8" s="10"/>
+      <c r="AX8" s="10"/>
+      <c r="AY8" s="10"/>
+      <c r="AZ8" s="10"/>
+      <c r="BA8" s="10"/>
+      <c r="BB8" s="10"/>
+      <c r="BC8" s="10"/>
+      <c r="BD8" s="10"/>
+      <c r="BE8" s="10"/>
+      <c r="BF8" s="10"/>
+      <c r="BG8" s="10"/>
+      <c r="BH8" s="10"/>
+      <c r="BI8" s="10"/>
+      <c r="BJ8" s="10"/>
+      <c r="BK8" s="10"/>
+      <c r="BL8" s="10"/>
+      <c r="BM8" s="10"/>
+      <c r="BN8" s="10"/>
+      <c r="BO8" s="10"/>
+      <c r="BP8" s="10"/>
+      <c r="BQ8" s="10"/>
+      <c r="BR8" s="10"/>
+      <c r="BS8" s="10"/>
+      <c r="BT8" s="10"/>
+      <c r="BU8" s="10"/>
+      <c r="BV8" s="10"/>
+      <c r="BW8" s="10"/>
+      <c r="BX8" s="10"/>
+      <c r="BY8" s="10"/>
+      <c r="BZ8" s="10"/>
+      <c r="CA8" s="10"/>
+      <c r="CB8" s="10"/>
+      <c r="CC8" s="10"/>
+      <c r="CD8" s="10"/>
+      <c r="CE8" s="10"/>
+      <c r="CF8" s="10"/>
+      <c r="CG8" s="10"/>
+      <c r="CH8" s="10"/>
+      <c r="CI8" s="10"/>
+      <c r="CJ8" s="10"/>
+      <c r="CK8" s="10"/>
+      <c r="CL8" s="10"/>
+      <c r="CM8" s="10"/>
+      <c r="CN8" s="10"/>
+      <c r="CO8" s="10"/>
+      <c r="CP8" s="10"/>
+      <c r="CQ8" s="10"/>
+      <c r="CR8" s="10"/>
+      <c r="CS8" s="10"/>
+      <c r="CT8" s="10"/>
+      <c r="CU8" s="10"/>
+      <c r="CV8" s="10"/>
+      <c r="CW8" s="10"/>
+      <c r="CX8" s="10"/>
+      <c r="CY8" s="10"/>
+      <c r="CZ8" s="10"/>
+      <c r="DA8" s="10"/>
+      <c r="DB8" s="10"/>
+      <c r="DC8" s="10"/>
+      <c r="DD8" s="10"/>
+      <c r="DE8" s="10"/>
+      <c r="DF8" s="10"/>
+      <c r="DG8" s="10"/>
+      <c r="DH8" s="10"/>
+      <c r="DI8" s="10"/>
+      <c r="DJ8" s="10"/>
+      <c r="DK8" s="10"/>
+      <c r="DL8" s="10"/>
+      <c r="DM8" s="10"/>
+      <c r="DN8" s="10"/>
+      <c r="DO8" s="10"/>
+      <c r="DP8" s="10"/>
+      <c r="DQ8" s="10"/>
     </row>
-    <row r="9" s="5" customFormat="1" spans="1:120">
+    <row r="9" s="5" customFormat="1" spans="1:121">
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -3784,8 +3875,9 @@
       <c r="DN9" s="10"/>
       <c r="DO9" s="10"/>
       <c r="DP9" s="10"/>
+      <c r="DQ9" s="10"/>
     </row>
-    <row r="10" s="5" customFormat="1" spans="1:120">
+    <row r="10" s="5" customFormat="1" spans="1:121">
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -3906,8 +3998,9 @@
       <c r="DN10" s="10"/>
       <c r="DO10" s="10"/>
       <c r="DP10" s="10"/>
+      <c r="DQ10" s="10"/>
     </row>
-    <row r="11" s="5" customFormat="1" spans="1:120">
+    <row r="11" s="5" customFormat="1" spans="1:121">
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -4028,8 +4121,9 @@
       <c r="DN11" s="10"/>
       <c r="DO11" s="10"/>
       <c r="DP11" s="10"/>
+      <c r="DQ11" s="10"/>
     </row>
-    <row r="12" s="5" customFormat="1" spans="1:120">
+    <row r="12" s="5" customFormat="1" spans="1:121">
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -4150,8 +4244,9 @@
       <c r="DN12" s="10"/>
       <c r="DO12" s="10"/>
       <c r="DP12" s="10"/>
+      <c r="DQ12" s="10"/>
     </row>
-    <row r="13" s="5" customFormat="1" spans="1:120">
+    <row r="13" s="5" customFormat="1" spans="1:121">
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -4272,8 +4367,9 @@
       <c r="DN13" s="10"/>
       <c r="DO13" s="10"/>
       <c r="DP13" s="10"/>
+      <c r="DQ13" s="10"/>
     </row>
-    <row r="14" s="5" customFormat="1" spans="1:120">
+    <row r="14" s="5" customFormat="1" spans="1:121">
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -4394,8 +4490,9 @@
       <c r="DN14" s="10"/>
       <c r="DO14" s="10"/>
       <c r="DP14" s="10"/>
+      <c r="DQ14" s="10"/>
     </row>
-    <row r="15" s="5" customFormat="1" spans="1:120">
+    <row r="15" s="5" customFormat="1" spans="1:121">
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -4516,8 +4613,9 @@
       <c r="DN15" s="10"/>
       <c r="DO15" s="10"/>
       <c r="DP15" s="10"/>
+      <c r="DQ15" s="10"/>
     </row>
-    <row r="16" s="5" customFormat="1" spans="1:120">
+    <row r="16" s="5" customFormat="1" spans="1:121">
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -4638,8 +4736,9 @@
       <c r="DN16" s="10"/>
       <c r="DO16" s="10"/>
       <c r="DP16" s="10"/>
+      <c r="DQ16" s="10"/>
     </row>
-    <row r="17" s="5" customFormat="1" spans="1:120">
+    <row r="17" s="5" customFormat="1" spans="1:121">
       <c r="A17" s="10"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -4760,8 +4859,9 @@
       <c r="DN17" s="10"/>
       <c r="DO17" s="10"/>
       <c r="DP17" s="10"/>
+      <c r="DQ17" s="10"/>
     </row>
-    <row r="18" s="5" customFormat="1" spans="1:120">
+    <row r="18" s="5" customFormat="1" spans="1:121">
       <c r="A18" s="10"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -4882,8 +4982,9 @@
       <c r="DN18" s="10"/>
       <c r="DO18" s="10"/>
       <c r="DP18" s="10"/>
+      <c r="DQ18" s="10"/>
     </row>
-    <row r="19" s="5" customFormat="1" spans="1:120">
+    <row r="19" s="5" customFormat="1" spans="1:121">
       <c r="A19" s="10"/>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -5004,8 +5105,9 @@
       <c r="DN19" s="10"/>
       <c r="DO19" s="10"/>
       <c r="DP19" s="10"/>
+      <c r="DQ19" s="10"/>
     </row>
-    <row r="20" s="5" customFormat="1" spans="1:120">
+    <row r="20" s="5" customFormat="1" spans="1:121">
       <c r="A20" s="10"/>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
@@ -5126,8 +5228,9 @@
       <c r="DN20" s="10"/>
       <c r="DO20" s="10"/>
       <c r="DP20" s="10"/>
+      <c r="DQ20" s="10"/>
     </row>
-    <row r="21" s="5" customFormat="1" spans="1:120">
+    <row r="21" s="5" customFormat="1" spans="1:121">
       <c r="A21" s="10"/>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
@@ -5248,8 +5351,9 @@
       <c r="DN21" s="10"/>
       <c r="DO21" s="10"/>
       <c r="DP21" s="10"/>
+      <c r="DQ21" s="10"/>
     </row>
-    <row r="22" s="5" customFormat="1" spans="1:120">
+    <row r="22" s="5" customFormat="1" spans="1:121">
       <c r="A22" s="10"/>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
@@ -5370,8 +5474,9 @@
       <c r="DN22" s="10"/>
       <c r="DO22" s="10"/>
       <c r="DP22" s="10"/>
+      <c r="DQ22" s="10"/>
     </row>
-    <row r="23" s="5" customFormat="1" spans="1:120">
+    <row r="23" s="5" customFormat="1" spans="1:121">
       <c r="A23" s="10"/>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
@@ -5492,250 +5597,7 @@
       <c r="DN23" s="10"/>
       <c r="DO23" s="10"/>
       <c r="DP23" s="10"/>
-    </row>
-    <row r="24" s="5" customFormat="1" spans="1:120">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
-      <c r="O24" s="10"/>
-      <c r="P24" s="10"/>
-      <c r="Q24" s="10"/>
-      <c r="R24" s="10"/>
-      <c r="S24" s="10"/>
-      <c r="T24" s="10"/>
-      <c r="U24" s="10"/>
-      <c r="V24" s="10"/>
-      <c r="W24" s="10"/>
-      <c r="X24" s="10"/>
-      <c r="Y24" s="10"/>
-      <c r="Z24" s="10"/>
-      <c r="AA24" s="10"/>
-      <c r="AB24" s="10"/>
-      <c r="AC24" s="10"/>
-      <c r="AD24" s="10"/>
-      <c r="AE24" s="10"/>
-      <c r="AF24" s="10"/>
-      <c r="AG24" s="10"/>
-      <c r="AH24" s="10"/>
-      <c r="AI24" s="10"/>
-      <c r="AJ24" s="10"/>
-      <c r="AK24" s="10"/>
-      <c r="AL24" s="10"/>
-      <c r="AM24" s="10"/>
-      <c r="AN24" s="10"/>
-      <c r="AO24" s="10"/>
-      <c r="AP24" s="10"/>
-      <c r="AQ24" s="10"/>
-      <c r="AR24" s="10"/>
-      <c r="AS24" s="10"/>
-      <c r="AT24" s="10"/>
-      <c r="AU24" s="10"/>
-      <c r="AV24" s="10"/>
-      <c r="AW24" s="10"/>
-      <c r="AX24" s="10"/>
-      <c r="AY24" s="10"/>
-      <c r="AZ24" s="10"/>
-      <c r="BA24" s="10"/>
-      <c r="BB24" s="10"/>
-      <c r="BC24" s="10"/>
-      <c r="BD24" s="10"/>
-      <c r="BE24" s="10"/>
-      <c r="BF24" s="10"/>
-      <c r="BG24" s="10"/>
-      <c r="BH24" s="10"/>
-      <c r="BI24" s="10"/>
-      <c r="BJ24" s="10"/>
-      <c r="BK24" s="10"/>
-      <c r="BL24" s="10"/>
-      <c r="BM24" s="10"/>
-      <c r="BN24" s="10"/>
-      <c r="BO24" s="10"/>
-      <c r="BP24" s="10"/>
-      <c r="BQ24" s="10"/>
-      <c r="BR24" s="10"/>
-      <c r="BS24" s="10"/>
-      <c r="BT24" s="10"/>
-      <c r="BU24" s="10"/>
-      <c r="BV24" s="10"/>
-      <c r="BW24" s="10"/>
-      <c r="BX24" s="10"/>
-      <c r="BY24" s="10"/>
-      <c r="BZ24" s="10"/>
-      <c r="CA24" s="10"/>
-      <c r="CB24" s="10"/>
-      <c r="CC24" s="10"/>
-      <c r="CD24" s="10"/>
-      <c r="CE24" s="10"/>
-      <c r="CF24" s="10"/>
-      <c r="CG24" s="10"/>
-      <c r="CH24" s="10"/>
-      <c r="CI24" s="10"/>
-      <c r="CJ24" s="10"/>
-      <c r="CK24" s="10"/>
-      <c r="CL24" s="10"/>
-      <c r="CM24" s="10"/>
-      <c r="CN24" s="10"/>
-      <c r="CO24" s="10"/>
-      <c r="CP24" s="10"/>
-      <c r="CQ24" s="10"/>
-      <c r="CR24" s="10"/>
-      <c r="CS24" s="10"/>
-      <c r="CT24" s="10"/>
-      <c r="CU24" s="10"/>
-      <c r="CV24" s="10"/>
-      <c r="CW24" s="10"/>
-      <c r="CX24" s="10"/>
-      <c r="CY24" s="10"/>
-      <c r="CZ24" s="10"/>
-      <c r="DA24" s="10"/>
-      <c r="DB24" s="10"/>
-      <c r="DC24" s="10"/>
-      <c r="DD24" s="10"/>
-      <c r="DE24" s="10"/>
-      <c r="DF24" s="10"/>
-      <c r="DG24" s="10"/>
-      <c r="DH24" s="10"/>
-      <c r="DI24" s="10"/>
-      <c r="DJ24" s="10"/>
-      <c r="DK24" s="10"/>
-      <c r="DL24" s="10"/>
-      <c r="DM24" s="10"/>
-      <c r="DN24" s="10"/>
-      <c r="DO24" s="10"/>
-      <c r="DP24" s="10"/>
-    </row>
-    <row r="25" s="5" customFormat="1" spans="1:120">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="10"/>
-      <c r="P25" s="10"/>
-      <c r="Q25" s="10"/>
-      <c r="R25" s="10"/>
-      <c r="S25" s="10"/>
-      <c r="T25" s="10"/>
-      <c r="U25" s="10"/>
-      <c r="V25" s="10"/>
-      <c r="W25" s="10"/>
-      <c r="X25" s="10"/>
-      <c r="Y25" s="10"/>
-      <c r="Z25" s="10"/>
-      <c r="AA25" s="10"/>
-      <c r="AB25" s="10"/>
-      <c r="AC25" s="10"/>
-      <c r="AD25" s="10"/>
-      <c r="AE25" s="10"/>
-      <c r="AF25" s="10"/>
-      <c r="AG25" s="10"/>
-      <c r="AH25" s="10"/>
-      <c r="AI25" s="10"/>
-      <c r="AJ25" s="10"/>
-      <c r="AK25" s="10"/>
-      <c r="AL25" s="10"/>
-      <c r="AM25" s="10"/>
-      <c r="AN25" s="10"/>
-      <c r="AO25" s="10"/>
-      <c r="AP25" s="10"/>
-      <c r="AQ25" s="10"/>
-      <c r="AR25" s="10"/>
-      <c r="AS25" s="10"/>
-      <c r="AT25" s="10"/>
-      <c r="AU25" s="10"/>
-      <c r="AV25" s="10"/>
-      <c r="AW25" s="10"/>
-      <c r="AX25" s="10"/>
-      <c r="AY25" s="10"/>
-      <c r="AZ25" s="10"/>
-      <c r="BA25" s="10"/>
-      <c r="BB25" s="10"/>
-      <c r="BC25" s="10"/>
-      <c r="BD25" s="10"/>
-      <c r="BE25" s="10"/>
-      <c r="BF25" s="10"/>
-      <c r="BG25" s="10"/>
-      <c r="BH25" s="10"/>
-      <c r="BI25" s="10"/>
-      <c r="BJ25" s="10"/>
-      <c r="BK25" s="10"/>
-      <c r="BL25" s="10"/>
-      <c r="BM25" s="10"/>
-      <c r="BN25" s="10"/>
-      <c r="BO25" s="10"/>
-      <c r="BP25" s="10"/>
-      <c r="BQ25" s="10"/>
-      <c r="BR25" s="10"/>
-      <c r="BS25" s="10"/>
-      <c r="BT25" s="10"/>
-      <c r="BU25" s="10"/>
-      <c r="BV25" s="10"/>
-      <c r="BW25" s="10"/>
-      <c r="BX25" s="10"/>
-      <c r="BY25" s="10"/>
-      <c r="BZ25" s="10"/>
-      <c r="CA25" s="10"/>
-      <c r="CB25" s="10"/>
-      <c r="CC25" s="10"/>
-      <c r="CD25" s="10"/>
-      <c r="CE25" s="10"/>
-      <c r="CF25" s="10"/>
-      <c r="CG25" s="10"/>
-      <c r="CH25" s="10"/>
-      <c r="CI25" s="10"/>
-      <c r="CJ25" s="10"/>
-      <c r="CK25" s="10"/>
-      <c r="CL25" s="10"/>
-      <c r="CM25" s="10"/>
-      <c r="CN25" s="10"/>
-      <c r="CO25" s="10"/>
-      <c r="CP25" s="10"/>
-      <c r="CQ25" s="10"/>
-      <c r="CR25" s="10"/>
-      <c r="CS25" s="10"/>
-      <c r="CT25" s="10"/>
-      <c r="CU25" s="10"/>
-      <c r="CV25" s="10"/>
-      <c r="CW25" s="10"/>
-      <c r="CX25" s="10"/>
-      <c r="CY25" s="10"/>
-      <c r="CZ25" s="10"/>
-      <c r="DA25" s="10"/>
-      <c r="DB25" s="10"/>
-      <c r="DC25" s="10"/>
-      <c r="DD25" s="10"/>
-      <c r="DE25" s="10"/>
-      <c r="DF25" s="10"/>
-      <c r="DG25" s="10"/>
-      <c r="DH25" s="10"/>
-      <c r="DI25" s="10"/>
-      <c r="DJ25" s="10"/>
-      <c r="DK25" s="10"/>
-      <c r="DL25" s="10"/>
-      <c r="DM25" s="10"/>
-      <c r="DN25" s="10"/>
-      <c r="DO25" s="10"/>
-      <c r="DP25" s="10"/>
+      <c r="DQ23" s="10"/>
     </row>
   </sheetData>
   <hyperlinks>
